--- a/w5-zone3-consumption-gating/poc/Zone3_Gating_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc/Zone3_Gating_Test_Tracker.xlsx
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>CLONE within the same schema, with COPY GRANTS</t>
+          <t>CLONE within the same schema, with COPY GRANTS — tags, grants AND owner</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R14, R18</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Clustering key survival — INSERT OVERWRITE vs CTAS</t>
+          <t>Clustering key survival — INSERT OVERWRITE vs CTAS vs CLONE</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">

--- a/w5-zone3-consumption-gating/poc/Zone3_Gating_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/poc/Zone3_Gating_Test_Tracker.xlsx
@@ -117,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -196,6 +196,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1762,7 +1765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1821,12 +1824,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Refresh a single-table consumption object</t>
+          <t>Refresh one object of a group (INSERT OVERWRITE in isolation)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>The consistency group contains exactly one table. No sibling has to agree with it.</t>
+          <t>Prove INSERT OVERWRITE never exposes an empty or partial table on its own. A consistency group always spans more than one object, so this is a property of the refresh statement, NOT a publication shape.</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -1841,7 +1844,7 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>O10 alone is sufficient — no staging, no swap, no privilege escalation</t>
+          <t>INSERT OVERWRITE is atomic per statement. It does NOT make a group atomic — that is what SC-02 and SC-03 decide.</t>
         </is>
       </c>
     </row>
@@ -2482,6 +2485,134 @@
       <c r="F23" s="8" t="inlineStr">
         <is>
           <t>INSERT OVERWRITE on Iceberg is not named in the documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>SC-22</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Mixed-cadence group — not every member is due</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>A group holding a weekly and a yearly dimension alongside daily facts. The gate must tell "due but missing" from "not due" (R22).</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>O11, gate</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>TC-042, TC-043</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Whether the gate can run at all on a real group. Without the expectation it blocks six days in seven, or passes a genuine failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>SC-23</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Publication re-run inside the same cycle</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>After an authorised partial release, the outstanding jobs complete and the normal publication path runs again for the same cycle.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>O11, gate</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>R12. Under A5 this is the whole of it: the publication step must be re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>SC-24</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Object not refreshed this cycle, published by swap</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>A swap exchanges the two storages, so an object never rewritten in staging flips back one version on every swap.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>O16, O11</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Whether O16 needs the PREPARE carry-forward clone, and confirms O11 does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>SC-25</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Publication by row access policy</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Both cycles live in the table; a row access policy admits only the cycle named in a marker table. Publication is one marker update.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>O12</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>TC-045, TC-046</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Whether O12 is a real fallback or only a theoretical one. Also supplies the row access policy R26 needs.</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4746,6 +4877,377 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr"/>
       <c r="O45" s="8" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Mixed-cadence group passes the gate: objects not due this cycle are stale, not missing</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>R22, R8</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>SC-22</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>O11, gate</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>04_gate_rollback_control.sql</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Design logic</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>G1, G2 and G2b all PASS. The group publishes with DIM_BROKER and DIM_DATE on their older cycle.</t>
+        </is>
+      </c>
+      <c r="I46" s="29" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="29" t="n"/>
+      <c r="L46" s="29" t="n"/>
+      <c r="M46" s="29" t="n"/>
+      <c r="N46" s="29" t="n"/>
+      <c r="O46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>An object that IS due but did not load fails the gate</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>R8, R9, R22</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>SC-22</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>O11, gate</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>04_gate_rollback_control.sql</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Design logic</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>G1 FAILs and names DIM_POLICY. Publication does not run.</t>
+        </is>
+      </c>
+      <c r="I47" s="29" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="J47" s="29" t="n"/>
+      <c r="K47" s="29" t="n"/>
+      <c r="L47" s="29" t="n"/>
+      <c r="M47" s="29" t="n"/>
+      <c r="N47" s="29" t="n"/>
+      <c r="O47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Schema swap moves an unrefreshed object backwards unless it is cloned forward</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>R1, R2, R22</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>SC-24</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>O16, O11</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>02_atomicity_publication.sql</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Not documented</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>ARM 1: DIM_BROKER regresses after the swap. ARM 2 (carry-forward first): unchanged.</t>
+        </is>
+      </c>
+      <c r="I48" s="29" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="29" t="n"/>
+      <c r="L48" s="29" t="n"/>
+      <c r="M48" s="29" t="n"/>
+      <c r="N48" s="29" t="n"/>
+      <c r="O48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Row access policy flips a whole group in one marker update; reader needs no grant on the marker table</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R26</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SC-25</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>O12</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>02_atomicity_publication.sql</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Not documented</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Reader sees only cycle 1 before, only cycle 2 after, never a mixture. Rollback by one more update.</t>
+        </is>
+      </c>
+      <c r="I49" s="29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J49" s="29" t="n"/>
+      <c r="K49" s="29" t="n"/>
+      <c r="L49" s="29" t="n"/>
+      <c r="M49" s="29" t="n"/>
+      <c r="N49" s="29" t="n"/>
+      <c r="O49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>A reader spanning the marker update sees one version</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>R1, R2, R6, R7</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>SC-25</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>O12</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>02_atomicity_publication.sql</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Inference, not documented</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>distinct_cycles_seen = 1. A result of 2 rules O12 out as a publication mechanism.</t>
+        </is>
+      </c>
+      <c r="I50" s="29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="29" t="n"/>
+      <c r="L50" s="29" t="n"/>
+      <c r="M50" s="29" t="n"/>
+      <c r="N50" s="29" t="n"/>
+      <c r="O50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Publication is re-runnable within a cycle after an authorised partial release</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>SC-23</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>O11, gate</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>04_gate_rollback_control.sql</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Design logic</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Second publication succeeds; every object on cycle 21; two PUBLICATION_LOG rows for the same cycle.</t>
+        </is>
+      </c>
+      <c r="I51" s="29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="29" t="n"/>
+      <c r="L51" s="29" t="n"/>
+      <c r="M51" s="29" t="n"/>
+      <c r="N51" s="29" t="n"/>
+      <c r="O51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Storage overhead of holding the previous published version alongside its replacement</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SC-20</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>O11, O16</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>05_sizing_performance.sql</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>No benchmark</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>A measured ratio (expect ~2x live, plus the Time Travel tail), not a pass/fail.</t>
+        </is>
+      </c>
+      <c r="I52" s="29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J52" s="29" t="n"/>
+      <c r="K52" s="29" t="n"/>
+      <c r="L52" s="29" t="n"/>
+      <c r="M52" s="29" t="n"/>
+      <c r="N52" s="29" t="n"/>
+      <c r="O52" s="3" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6404,7 +6906,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TC-020, TC-025</t>
+          <t>TC-020, TC-025, TC-044, TC-045, TC-046</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6427,7 +6929,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TC-020, TC-023, TC-025, TC-026</t>
+          <t>TC-020, TC-023, TC-025, TC-026, TC-044, TC-045, TC-046</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6450,7 +6952,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TC-020, TC-023, TC-027, TC-032</t>
+          <t>TC-020, TC-023, TC-027, TC-032, TC-045</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6523,7 +7025,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TC-020, TC-023</t>
+          <t>TC-020, TC-023, TC-046</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6546,7 +7048,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-020, TC-046</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6569,7 +7071,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TC-034</t>
+          <t>TC-034, TC-042, TC-043</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6592,7 +7094,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TC-024, TC-034</t>
+          <t>TC-024, TC-034, TC-043</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6661,17 +7163,17 @@
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-047</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>NO TEST</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Reduces to "publication is re-runnable within a cycle" under assumption A5. Worth one test.</t>
+          <t>Reduces to "publication is re-runnable within a cycle" under A5. TC-047 tests exactly that.</t>
         </is>
       </c>
     </row>
@@ -6899,7 +7401,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TC-040, TC-041</t>
+          <t>TC-040, TC-041, TC-042, TC-043</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6907,7 +7409,11 @@
           <t>Covered</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr"/>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>Extended 2026-10-25 to carry a per-cycle refresh expectation. TC-042/043 test the distinction the gate must make.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6945,17 +7451,17 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-048</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>NO TEST</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Storage overhead not measured. TC-052/053 time the publish, they do not size the retained copy.</t>
+          <t>TC-048 measures the retained copy and the Time Travel tail. TC-052/053 time the publish only.</t>
         </is>
       </c>
     </row>
@@ -6995,17 +7501,17 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-045</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>NO TEST</t>
+          <t>Covered</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>No row access policy exists in the POC fixture. Add one, or record that none exists in Zone 3.</t>
+          <t>The O12 fixture supplies the row access policy the pack previously lacked.</t>
         </is>
       </c>
     </row>
